--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_BISON_HUNTER_CHOICE.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_BISON_HUNTER_CHOICE.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26.35" customWidth="1" min="1" max="1"/>
@@ -537,6 +537,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -605,10 +606,15 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Average Harvest Age Prior Year</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>Avg Days Hunted Prior Year</t>
         </is>
@@ -665,7 +671,8 @@
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -734,7 +741,8 @@
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr"/>
-      <c r="O5" s="6" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -803,7 +811,8 @@
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
@@ -872,7 +881,8 @@
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr"/>
-      <c r="O7" s="6" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" s="6" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -941,7 +951,8 @@
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr"/>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1010,7 +1021,8 @@
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr"/>
-      <c r="O9" s="6" t="inlineStr">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" s="6" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -1067,7 +1079,8 @@
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr"/>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -1136,7 +1149,8 @@
         </is>
       </c>
       <c r="N11" s="6" t="inlineStr"/>
-      <c r="O11" s="6" t="inlineStr">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1205,7 +1219,8 @@
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr"/>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" s="4" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -1274,7 +1289,8 @@
         </is>
       </c>
       <c r="N13" s="6" t="inlineStr"/>
-      <c r="O13" s="6" t="inlineStr">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1343,7 +1359,8 @@
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr"/>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
@@ -1412,7 +1429,8 @@
         </is>
       </c>
       <c r="N15" s="6" t="inlineStr"/>
-      <c r="O15" s="6" t="inlineStr">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" s="6" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -1481,7 +1499,8 @@
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr"/>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" s="4" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -1538,7 +1557,8 @@
       </c>
       <c r="M17" s="6" t="inlineStr"/>
       <c r="N17" s="6" t="inlineStr"/>
-      <c r="O17" s="6" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:O17"/>
